--- a/artfynd/A 25914-2026 artfynd.xlsx
+++ b/artfynd/A 25914-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136117116</v>
       </c>
       <c r="B2" t="n">
-        <v>79553</v>
+        <v>79555</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136117374</v>
       </c>
       <c r="B3" t="n">
-        <v>79553</v>
+        <v>79555</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136117510</v>
       </c>
       <c r="B4" t="n">
-        <v>79553</v>
+        <v>79555</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136117908</v>
       </c>
       <c r="B5" t="n">
-        <v>79553</v>
+        <v>79555</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136118481</v>
       </c>
       <c r="B6" t="n">
-        <v>79553</v>
+        <v>79555</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136117349</v>
       </c>
       <c r="B7" t="n">
-        <v>83341</v>
+        <v>83343</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136117345</v>
       </c>
       <c r="B8" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136117477</v>
       </c>
       <c r="B9" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136118002</v>
       </c>
       <c r="B10" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136118386</v>
       </c>
       <c r="B11" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136119149</v>
       </c>
       <c r="B12" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136117980</v>
       </c>
       <c r="B13" t="n">
-        <v>83461</v>
+        <v>83463</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136118686</v>
       </c>
       <c r="B14" t="n">
-        <v>83461</v>
+        <v>83463</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136118832</v>
       </c>
       <c r="B15" t="n">
-        <v>83461</v>
+        <v>83463</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136118505</v>
       </c>
       <c r="B16" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>136118572</v>
       </c>
       <c r="B17" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2325,7 +2325,7 @@
         <v>136119113</v>
       </c>
       <c r="B18" t="n">
-        <v>58110</v>
+        <v>58112</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>136117408</v>
       </c>
       <c r="B21" t="n">
-        <v>80064</v>
+        <v>80066</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
